--- a/Resultados/- Hash Perceptual.xlsx
+++ b/Resultados/- Hash Perceptual.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\Resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F3A4DDE-6693-4069-A49D-DB589EDDC6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B02F177-B8AB-42A3-9E9D-FB56C72DCAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" firstSheet="1" activeTab="4" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="22" r:id="rId1"/>
     <sheet name="MountainDatabase" sheetId="23" r:id="rId2"/>
     <sheet name="PalaceDatabase" sheetId="24" r:id="rId3"/>
     <sheet name="WashingtonDatabase" sheetId="2" r:id="rId4"/>
+    <sheet name="ParkDatabase" sheetId="25" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">LennaDatabase!$A$1:$B$1</definedName>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="431">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -990,6 +991,351 @@
   </si>
   <si>
     <t>3ffffcf4f4f4f5e4</t>
+  </si>
+  <si>
+    <t>e6ce8e9938149694</t>
+  </si>
+  <si>
+    <t>00006000000</t>
+  </si>
+  <si>
+    <t>e6ce8e9918149694</t>
+  </si>
+  <si>
+    <t>08033000000</t>
+  </si>
+  <si>
+    <t>00016000000</t>
+  </si>
+  <si>
+    <t>0803a000000</t>
+  </si>
+  <si>
+    <t>e6ce8e891c549694</t>
+  </si>
+  <si>
+    <t>09033000000</t>
+  </si>
+  <si>
+    <t>e6ce8e993c149694</t>
+  </si>
+  <si>
+    <t>0001a000040</t>
+  </si>
+  <si>
+    <t>e6ce8e891c149694</t>
+  </si>
+  <si>
+    <t>0b017000000</t>
+  </si>
+  <si>
+    <t>081d0000000</t>
+  </si>
+  <si>
+    <t>b0808080c0c0e8d1</t>
+  </si>
+  <si>
+    <t>90d0b0b0f0dcb331</t>
+  </si>
+  <si>
+    <t>f8fcd8d8f8f8f8d1</t>
+  </si>
+  <si>
+    <t>08180001000</t>
+  </si>
+  <si>
+    <t>08031000000</t>
+  </si>
+  <si>
+    <t>08038000000</t>
+  </si>
+  <si>
+    <t>0f070000000</t>
+  </si>
+  <si>
+    <t>f5a1854f4a60b735</t>
+  </si>
+  <si>
+    <t>e6ce8e8918149694</t>
+  </si>
+  <si>
+    <t>18200019000</t>
+  </si>
+  <si>
+    <t>0b038000000</t>
+  </si>
+  <si>
+    <t>09038000000</t>
+  </si>
+  <si>
+    <t>3f7f6fef070e0202</t>
+  </si>
+  <si>
+    <t>91e3051f4ae0373f</t>
+  </si>
+  <si>
+    <t>eecede9d3e7cb6b6</t>
+  </si>
+  <si>
+    <t>3f7f6f67070e0202</t>
+  </si>
+  <si>
+    <t>91e7051f48e0373f</t>
+  </si>
+  <si>
+    <t>eecede9d3e7cb6b4</t>
+  </si>
+  <si>
+    <t>07007000000</t>
+  </si>
+  <si>
+    <t>00030000000</t>
+  </si>
+  <si>
+    <t>eede9e99bcbcb6b4</t>
+  </si>
+  <si>
+    <t>3f7f6fcf07060202</t>
+  </si>
+  <si>
+    <t>b1e3051f48e0373f</t>
+  </si>
+  <si>
+    <t>e6cece9d3c7cf6b6</t>
+  </si>
+  <si>
+    <t>3f7f6fe707060202</t>
+  </si>
+  <si>
+    <t>e6cede9d3e7cf6b6</t>
+  </si>
+  <si>
+    <t>eecede9d3c7cf6b6</t>
+  </si>
+  <si>
+    <t>0100e000000</t>
+  </si>
+  <si>
+    <t>3f7f6fef070f0202</t>
+  </si>
+  <si>
+    <t>e6cedc9d3c7cb6b6</t>
+  </si>
+  <si>
+    <t>0f03a000000</t>
+  </si>
+  <si>
+    <t>1ee00000000</t>
+  </si>
+  <si>
+    <t>e6ce8e991c14b694</t>
+  </si>
+  <si>
+    <t>12007000000</t>
+  </si>
+  <si>
+    <t>170b0000000</t>
+  </si>
+  <si>
+    <t>17047000000</t>
+  </si>
+  <si>
+    <t>17c40000000</t>
+  </si>
+  <si>
+    <t>b0b43c3c383836b2</t>
+  </si>
+  <si>
+    <t>eecede9d3e7eb6b6</t>
+  </si>
+  <si>
+    <t>8101858101810929</t>
+  </si>
+  <si>
+    <t>fffde8c1e5600000</t>
+  </si>
+  <si>
+    <t>e3e994e5b5acc091</t>
+  </si>
+  <si>
+    <t>4659d98bcbcb9639</t>
+  </si>
+  <si>
+    <t>fffdf9e1e5600000</t>
+  </si>
+  <si>
+    <t>01380002000</t>
+  </si>
+  <si>
+    <t>013c0001000</t>
+  </si>
+  <si>
+    <t>01380001000</t>
+  </si>
+  <si>
+    <t>4659d98bcbcb9e39</t>
+  </si>
+  <si>
+    <t>02380001000</t>
+  </si>
+  <si>
+    <t>fffdf9e1c1400000</t>
+  </si>
+  <si>
+    <t>e9cb94e5a5acc0c5</t>
+  </si>
+  <si>
+    <t>4659d98b8b8b9a39</t>
+  </si>
+  <si>
+    <t>fffdf9e1e1414000</t>
+  </si>
+  <si>
+    <t>4659d98b8b8b9c39</t>
+  </si>
+  <si>
+    <t>e9cb94e5a5ac90c5</t>
+  </si>
+  <si>
+    <t>4659998b8b8b9a39</t>
+  </si>
+  <si>
+    <t>9eb631326a3236b2</t>
+  </si>
+  <si>
+    <t>5c5525c5476ee6e6</t>
+  </si>
+  <si>
+    <t>3c64e8a2c68c86a4</t>
+  </si>
+  <si>
+    <t>9432307939b9b9f9</t>
+  </si>
+  <si>
+    <t>2c0d1e968f8f27a3</t>
+  </si>
+  <si>
+    <t>713317ce9b3574f0</t>
+  </si>
+  <si>
+    <t>b1c0a0b4e4d6d8c2</t>
+  </si>
+  <si>
+    <t>1c2ca94bcd8c8d93</t>
+  </si>
+  <si>
+    <t>eb37c7f3b97939b9</t>
+  </si>
+  <si>
+    <t>59c936b8ecb2d24b</t>
+  </si>
+  <si>
+    <t>9432307979b8b9f9</t>
+  </si>
+  <si>
+    <t>713317ce9a3474f0</t>
+  </si>
+  <si>
+    <t>171617662c0f3b7c</t>
+  </si>
+  <si>
+    <t>4c5455a72724c54b</t>
+  </si>
+  <si>
+    <t>3c64e8a2c68886a4</t>
+  </si>
+  <si>
+    <t>5ac97eb8ec92d363</t>
+  </si>
+  <si>
+    <t>94b2307939b8b1f9</t>
+  </si>
+  <si>
+    <t>0c9e1e4e4fc7a783</t>
+  </si>
+  <si>
+    <t>713317c6db3474f0</t>
+  </si>
+  <si>
+    <t>9eb639326a3236b2</t>
+  </si>
+  <si>
+    <t>4c5455a72524c54b</t>
+  </si>
+  <si>
+    <t>3c64e8a2c688c4a4</t>
+  </si>
+  <si>
+    <t>5bc97eb8ec92d343</t>
+  </si>
+  <si>
+    <t>0e9e1e0e0fc7a783</t>
+  </si>
+  <si>
+    <t>e327c7f3b97939b9</t>
+  </si>
+  <si>
+    <t>3464e8d2e6888cb4</t>
+  </si>
+  <si>
+    <t>49c936e8ac925b63</t>
+  </si>
+  <si>
+    <t>94b0307939b8b1f8</t>
+  </si>
+  <si>
+    <t>9e9e1ece4fc7e743</t>
+  </si>
+  <si>
+    <t>713317ce9a3174f0</t>
+  </si>
+  <si>
+    <t>9eb639326a3030b2</t>
+  </si>
+  <si>
+    <t>b1c9a1b4e4d4d8c6</t>
+  </si>
+  <si>
+    <t>1c2cab4bcd0c8d93</t>
+  </si>
+  <si>
+    <t>5ac97eb8ec92d263</t>
+  </si>
+  <si>
+    <t>913556d4b9244125</t>
+  </si>
+  <si>
+    <t>0c9e1e4e4fc7a792</t>
+  </si>
+  <si>
+    <t>9eb631326a3030b2</t>
+  </si>
+  <si>
+    <t>b1345694b9644325</t>
+  </si>
+  <si>
+    <t>3c6ce8e28688cca4</t>
+  </si>
+  <si>
+    <t>5bc97ed8ec92d36b</t>
+  </si>
+  <si>
+    <t>b134569cb0644125</t>
+  </si>
+  <si>
+    <t>2c2c1e9e8f8f2707</t>
+  </si>
+  <si>
+    <t>713317ce9b3474f0</t>
+  </si>
+  <si>
+    <t>3c64e8a2c6888ea4</t>
+  </si>
+  <si>
+    <t>0e9e1e4e4fc7a783</t>
+  </si>
+  <si>
+    <t>713317c6db3574f0</t>
   </si>
 </sst>
 </file>
@@ -3590,7 +3936,7 @@
     <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
@@ -3707,436 +4053,1016 @@
       <c r="A4" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="B7" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="B8" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="B9" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+      <c r="B11" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+      <c r="B12" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
+      <c r="B14" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
+      <c r="B15" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
+      <c r="B17" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
+      <c r="B18" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
+      <c r="B19" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
+      <c r="B20" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
+      <c r="B21" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
+      <c r="B22" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
+      <c r="B23" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
+      <c r="B24" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
+      <c r="B25" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
+      <c r="B26" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
+      <c r="B27" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
+      <c r="B28" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
+      <c r="B29" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
+      <c r="B30" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
+      <c r="B31" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
+      <c r="B32" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -4571,4 +5497,593 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5336A-CE30-47EF-AA56-D1E814810829}">
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="17.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>